--- a/lojas-proprias/pwr_reports/Keys Summary - Lojas Corporativas (Stores)(2026-08-24 - 2026-08-30).xlsx
+++ b/lojas-proprias/pwr_reports/Keys Summary - Lojas Corporativas (Stores)(2026-08-24 - 2026-08-30).xlsx
@@ -204,7 +204,7 @@
   </si>
   <si>
     <t>22
-21</t>
+20</t>
   </si>
   <si>
     <t>14</t>
@@ -214,11 +214,11 @@
   </si>
   <si>
     <t>R$ 54.043,52
-R$ 51.470,02</t>
-  </si>
-  <si>
-    <t>1.6%
-2.7%</t>
+R$ 51.779,54</t>
+  </si>
+  <si>
+    <t>2.9%
+(1.4%)</t>
   </si>
   <si>
     <t>587.8</t>
@@ -227,7 +227,7 @@
     <t>(0.2%)</t>
   </si>
   <si>
-    <t>31.1%</t>
+    <t>31.0%</t>
   </si>
   <si>
     <t>(1.1%)</t>
@@ -915,7 +915,7 @@
         <v>68437.169999999998</v>
       </c>
       <c r="Q2" s="6">
-        <v>0.045141950623400096</v>
+        <v>-0.0094783697979724524</v>
       </c>
       <c r="R2" s="7">
         <v>612</v>
@@ -1046,7 +1046,7 @@
         <v>49668.5</v>
       </c>
       <c r="Q3" s="6">
-        <v>0.022396027705772426</v>
+        <v>-0.025861061272777208</v>
       </c>
       <c r="R3" s="7">
         <v>555</v>
@@ -1177,7 +1177,7 @@
         <v>47797.003333333334</v>
       </c>
       <c r="Q4" s="6">
-        <v>-0.27841631537579381</v>
+        <v>-0.0058505273967749405</v>
       </c>
       <c r="R4" s="7">
         <v>501.66666666666669</v>
@@ -1302,13 +1302,13 @@
         <v>52</v>
       </c>
       <c r="O5" s="5">
-        <v>55015.010000000009</v>
+        <v>55015.010000000002</v>
       </c>
       <c r="P5" s="5">
-        <v>55015.010000000009</v>
+        <v>55015.010000000002</v>
       </c>
       <c r="Q5" s="6">
-        <v>-0.035536735148249954</v>
+        <v>-0.088844403503314906</v>
       </c>
       <c r="R5" s="7">
         <v>607</v>
@@ -1344,7 +1344,7 @@
         <v>3.9723646723646722</v>
       </c>
       <c r="AC5" s="8">
-        <v>9.8989170000000009</v>
+        <v>9.4672249999999991</v>
       </c>
       <c r="AD5" s="8">
         <v>16.375470903954803</v>
@@ -1441,7 +1441,7 @@
         <v>51431.290000000001</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.10843918521957252</v>
+        <v>0.054263376796948259</v>
       </c>
       <c r="R6" s="7">
         <v>596</v>
@@ -1566,13 +1566,13 @@
         <v>52</v>
       </c>
       <c r="O7" s="5">
-        <v>62066.010000000002</v>
+        <v>62066.009999999995</v>
       </c>
       <c r="P7" s="5">
-        <v>62066.010000000002</v>
+        <v>62066.009999999995</v>
       </c>
       <c r="Q7" s="6">
-        <v>-0.069746517732607649</v>
+        <v>-0.12302489528820604</v>
       </c>
       <c r="R7" s="7">
         <v>626</v>
@@ -1701,7 +1701,7 @@
         <v>48332.869999999995</v>
       </c>
       <c r="Q8" s="6">
-        <v>0.13039777909788697</v>
+        <v>0.072747159430769592</v>
       </c>
       <c r="R8" s="7">
         <v>456</v>
@@ -1737,7 +1737,7 @@
         <v>3.5149091836734692</v>
       </c>
       <c r="AC8" s="8">
-        <v>13.338536</v>
+        <v>13.868258000000001</v>
       </c>
       <c r="AD8" s="8">
         <v>20.804721160409557</v>
@@ -1826,13 +1826,13 @@
         <v>52</v>
       </c>
       <c r="O9" s="5">
-        <v>26463.75</v>
+        <v>26463.749999999996</v>
       </c>
       <c r="P9" s="5">
-        <v>46311.5625</v>
+        <v>46311.562499999993</v>
       </c>
       <c r="Q9" s="6">
-        <v>-0.30934661413046161</v>
+        <v>0.040379153850508276</v>
       </c>
       <c r="R9" s="7">
         <v>493.5</v>
@@ -1957,13 +1957,13 @@
         <v>52</v>
       </c>
       <c r="O10" s="5">
-        <v>82771.050000000003</v>
+        <v>82771.049999999988</v>
       </c>
       <c r="P10" s="5">
-        <v>82771.050000000003</v>
+        <v>82771.049999999974</v>
       </c>
       <c r="Q10" s="6">
-        <v>-0.091259569402811214</v>
+        <v>-0.098792809248313351</v>
       </c>
       <c r="R10" s="7">
         <v>923</v>
@@ -2088,13 +2088,13 @@
         <v>52</v>
       </c>
       <c r="O11" s="5">
-        <v>116572.63999999998</v>
+        <v>116572.64</v>
       </c>
       <c r="P11" s="5">
-        <v>116572.63999999998</v>
+        <v>116572.64</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.098543541606453067</v>
+        <v>0.04105292120943016</v>
       </c>
       <c r="R11" s="7">
         <v>1298</v>
@@ -2130,7 +2130,7 @@
         <v>3.4437280263157892</v>
       </c>
       <c r="AC11" s="8">
-        <v>10.027253</v>
+        <v>10.467662000000001</v>
       </c>
       <c r="AD11" s="8">
         <v>17.398189267015706</v>
@@ -2225,7 +2225,7 @@
         <v>37017.330000000002</v>
       </c>
       <c r="Q12" s="6">
-        <v>0.19827238223178956</v>
+        <v>0.14384467063425843</v>
       </c>
       <c r="R12" s="7">
         <v>378</v>
@@ -2356,7 +2356,7 @@
         <v>79931.489999999991</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.00223150025227703</v>
+        <v>-0.041222927167527179</v>
       </c>
       <c r="R13" s="7">
         <v>926</v>
@@ -2392,7 +2392,7 @@
         <v>2.970661717352415</v>
       </c>
       <c r="AC13" s="8">
-        <v>11.670938</v>
+        <v>10.989013999999999</v>
       </c>
       <c r="AD13" s="8">
         <v>15.798382835820895</v>
@@ -2483,13 +2483,13 @@
         <v>52</v>
       </c>
       <c r="O14" s="5">
-        <v>33928.070000000007</v>
+        <v>33928.07</v>
       </c>
       <c r="P14" s="5">
-        <v>33928.070000000007</v>
+        <v>33928.07</v>
       </c>
       <c r="Q14" s="6">
-        <v>0.098271604778417121</v>
+        <v>0.050089617077724968</v>
       </c>
       <c r="R14" s="7">
         <v>357</v>
@@ -2525,7 +2525,7 @@
         <v>3.8755694779116467</v>
       </c>
       <c r="AC14" s="8">
-        <v>10.128091</v>
+        <v>9.4364849999999993</v>
       </c>
       <c r="AD14" s="8">
         <v>16.252221960784315</v>
@@ -2717,7 +2717,7 @@
         <v>36525.480000000003</v>
       </c>
       <c r="Q16" s="6">
-        <v>0.1018879217475277</v>
+        <v>0.043753037988682353</v>
       </c>
       <c r="R16" s="7">
         <v>426</v>
@@ -2848,7 +2848,7 @@
         <v>32544.5</v>
       </c>
       <c r="Q17" s="6">
-        <v>-0.050719402111755407</v>
+        <v>-0.09770473295725346</v>
       </c>
       <c r="R17" s="7">
         <v>356</v>
@@ -2857,10 +2857,10 @@
         <v>-0.16431924882629112</v>
       </c>
       <c r="T17" s="6">
-        <v>0.34735086112860852</v>
+        <v>0.34682112492126166</v>
       </c>
       <c r="U17" s="6">
-        <v>-0.0038230699503756394</v>
+        <v>-0.0043528061577225025</v>
       </c>
       <c r="V17" s="6">
         <v>0.026098695632134464</v>
@@ -2884,7 +2884,7 @@
         <v>3.370098319327731</v>
       </c>
       <c r="AC17" s="8">
-        <v>7.1565079999999996</v>
+        <v>7.3176769999999998</v>
       </c>
       <c r="AD17" s="8">
         <v>14.178472083333332</v>
@@ -2977,7 +2977,7 @@
         <v>60959.389999999999</v>
       </c>
       <c r="Q18" s="6">
-        <v>0.0065801542876928742</v>
+        <v>-0.046649579378398642</v>
       </c>
       <c r="R18" s="7">
         <v>750</v>
@@ -3013,7 +3013,7 @@
         <v>4.2159998333333339</v>
       </c>
       <c r="AC18" s="8">
-        <v>6.2873080000000003</v>
+        <v>6.2898839999999998</v>
       </c>
       <c r="AD18" s="8">
         <v>13.200746434494196</v>
@@ -3108,7 +3108,7 @@
         <v>58684.400000000001</v>
       </c>
       <c r="Q19" s="6">
-        <v>-0.045700028506516999</v>
+        <v>-0.095270801006104189</v>
       </c>
       <c r="R19" s="7">
         <v>560</v>
@@ -3239,7 +3239,7 @@
         <v>35342.449999999997</v>
       </c>
       <c r="Q20" s="6">
-        <v>-0.059093059468704134</v>
+        <v>-0.10350387985451093</v>
       </c>
       <c r="R20" s="7">
         <v>441</v>
@@ -3370,7 +3370,7 @@
         <v>28244.759999999998</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.2263769014539494</v>
+        <v>0.16849178263427311</v>
       </c>
       <c r="R21" s="7">
         <v>375</v>
@@ -3379,10 +3379,10 @@
         <v>0.40449438202247201</v>
       </c>
       <c r="T21" s="6">
-        <v>0.33890536156087009</v>
+        <v>0.32458624537790376</v>
       </c>
       <c r="U21" s="6">
-        <v>0.022404176916355462</v>
+        <v>0.0080850607333891322</v>
       </c>
       <c r="V21" s="6">
         <v>0.11089864102226396</v>
@@ -3497,14 +3497,12 @@
         <v>52</v>
       </c>
       <c r="O22" s="5">
-        <v>45279.720000000001</v>
+        <v>45279.720000000008</v>
       </c>
       <c r="P22" s="5">
         <v>45279.720000000008</v>
       </c>
-      <c r="Q22" s="6">
-        <v>-0.081067478233057266</v>
-      </c>
+      <c r="Q22" s="6"/>
       <c r="R22" s="7">
         <v>464.00000000000006</v>
       </c>
@@ -3512,10 +3510,10 @@
         <v>-0.15636363636363626</v>
       </c>
       <c r="T22" s="6">
-        <v>0.31643594748377418</v>
+        <v>0.31539795519936958</v>
       </c>
       <c r="U22" s="6">
-        <v>-0.0091422583885236042</v>
+        <v>-0.010180250672928191</v>
       </c>
       <c r="V22" s="6">
         <v>0.020658122444220061</v>
@@ -3634,7 +3632,7 @@
         <v>51170.120000000003</v>
       </c>
       <c r="Q23" s="6">
-        <v>0.24227573115536227</v>
+        <v>0.17630999523224311</v>
       </c>
       <c r="R23" s="7">
         <v>553</v>
